--- a/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:51</t>
+          <t>2026-08-31 01:36:38</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:52</t>
+          <t>2026-08-31 01:36:39</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:53</t>
+          <t>2026-08-31 01:36:40</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:55</t>
+          <t>2026-08-31 01:36:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:55</t>
+          <t>2026-08-31 01:36:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:55</t>
+          <t>2026-08-31 01:36:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:55</t>
+          <t>2026-08-31 01:36:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:40:55</t>
+          <t>2026-08-31 01:36:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3360</v>
+        <v>3425</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.20%803,000</t>
+          <t>7.90%658,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.20%</t>
+          <t>7.90%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>803000</v>
+        <v>658000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6015</v>
+        <v>6100</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.59%419,000</t>
+          <t>7.78%364,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.59%</t>
+          <t>7.78%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>419000</v>
+        <v>364000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,33 +631,33 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5785</v>
+        <v>5990</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.42%427,000</t>
+          <t>7.76%370,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>7.76%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>427000</v>
+        <v>370000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3985</v>
+        <v>3925</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.52%480,000</t>
+          <t>6.60%480,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>6.60%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1110</v>
+        <v>999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.94%1,570,000</t>
+          <t>5.49%1,570,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.61%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2260</v>
+        <v>2170</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.12%665,000</t>
+          <t>5.06%665,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.12%</t>
+          <t>5.06%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.68%273,000</t>
+          <t>4.91%273,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+9.71%1130</t>
+          <t>+3.1%1165</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+9.71%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1130</v>
+        <v>1165</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.34%1,127,000</t>
+          <t>4.60%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.34%</t>
+          <t>4.60%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5490</v>
+        <v>5485</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.97%212,000</t>
+          <t>4.07%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>4.07%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.83%529,000</t>
+          <t>3.77%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.77%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.12%739,000</t>
+          <t>3.18%739,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.18%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+2.78%16065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>15630</v>
+        <v>16065</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.89%54,300</t>
+          <t>3.06%54,300</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.29%6490</t>
+          <t>-9.71%5860</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6490</v>
+        <v>5860</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.65%120,000</t>
+          <t>2.46%120,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.4%895</t>
+          <t>+6.16%2845</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>895</v>
+        <v>2845</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.29%750,000</t>
+          <t>2.44%245,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>750000</v>
+        <v>245000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:38</t>
+          <t>2026-08-31 19:31:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.19%2680</t>
+          <t>+3.58%927</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>+3.58%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2680</v>
+        <v>927</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.24%245,000</t>
+          <t>2.44%750,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>245000</v>
+        <v>750000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>4991環宇-KY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>+3.65%539</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>+3.65%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2345</v>
+        <v>539</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.17%271,000</t>
+          <t>2.27%1,200,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.27%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>271000</v>
+        <v>1200000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4991環宇-KY</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.35%520</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>520</v>
+        <v>2305</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.13%1,200,000</t>
+          <t>2.19%271,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1200000</v>
+        <v>271000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.28%14300</t>
+          <t>-0.84%14180</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14300</v>
+        <v>14180</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.05%42,000</t>
+          <t>2.09%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.93%3305</t>
+          <t>+6.81%3530</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+6.81%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3305</v>
+        <v>3530</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.78%158,400</t>
+          <t>1.96%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.55%306,000</t>
+          <t>1.54%306,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7734印能科技</t>
+          <t>2330台積電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.36%2995</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.36%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2995</v>
+        <v>2405</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.53%150,000</t>
+          <t>1.51%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.51%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>150000</v>
+        <v>179000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2330台積電</t>
+          <t>7734印能科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-5.68%2825</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-5.68%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2420</v>
+        <v>2825</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%179,000</t>
+          <t>1.48%150,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>179000</v>
+        <v>150000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+9.86%635</t>
+          <t>+1.73%646</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+9.86%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.41%650,000</t>
+          <t>1.47%650,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.2%2485</t>
+          <t>-3.02%2410</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-3.02%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2485</v>
+        <v>2410</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.29%152,000</t>
+          <t>1.28%152,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7200</v>
+        <v>7095</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.23%50,000</t>
+          <t>1.24%50,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,25 +2034,25 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.44%1265</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1265</v>
+        <v>1175</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.22%282,000</t>
+          <t>1.16%282,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.18%201.5</t>
+          <t>-0.99%199.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>201.5</v>
+        <v>199.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.96%1,400,000</t>
+          <t>0.98%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.55%1365</t>
+          <t>-1.47%1345</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1365</v>
+        <v>1345</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.92%198,000</t>
+          <t>0.93%198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.59%94,000</t>
+          <t>0.61%94,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:39</t>
+          <t>2026-08-31 19:31:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.13%990</t>
+          <t>-2.12%969</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>990</v>
+        <v>969</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.55%620</t>
+          <t>-0.32%618</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.55%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.53%250,000</t>
+          <t>0.54%250,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.38%6250</t>
+          <t>+0.56%6285</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6250</v>
+        <v>6285</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.49%23,000</t>
+          <t>0.51%23,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.46%972</t>
+          <t>-6.17%912</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-6.17%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>972</v>
+        <v>912</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.36%110,000</t>
+          <t>0.35%110,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.82%247</t>
+          <t>-1.21%244</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.64%620</t>
+          <t>-2.1%607</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.64%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.13%790</t>
+          <t>-2.66%769</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>790</v>
+        <v>769</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.32%153</t>
+          <t>-0.98%151.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>153</v>
+        <v>151.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.23%216</t>
+          <t>+0.23%216.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>216</v>
+        <v>216.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+9.09%270</t>
+          <t>-4.81%257</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+9.09%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>-0.77%129</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.03%78,000</t>
+          <t>0.04%78,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.84%754</t>
+          <t>-1.72%741</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+7.06%235</t>
+          <t>-2.98%228</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+7.46%454</t>
+          <t>-4.19%435</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>-4.19%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+5.04%4065</t>
+          <t>+0.25%4075</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4065</v>
+        <v>4075</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:40</t>
+          <t>2026-08-31 19:31:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.89%669</t>
+          <t>+1.2%677</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.89%</t>
+          <t>+1.2%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:41</t>
+          <t>2026-08-31 19:31:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:41</t>
+          <t>2026-08-31 19:31:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+6.77%1735</t>
+          <t>-2.59%1690</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+6.77%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:41</t>
+          <t>2026-08-31 19:31:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+5.96%1510</t>
+          <t>+0.71%1425</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1510</v>
+        <v>1425</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:41</t>
+          <t>2026-08-31 19:31:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.39%1415</t>
+          <t>-8.61%1380</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>-8.61%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1415</v>
+        <v>1380</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:41</t>
+          <t>2026-08-31 19:31:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.2%249</t>
+          <t>-3.21%241</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:15</t>
+          <t>2026-08-31 22:23:14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:16</t>
+          <t>2026-08-31 22:23:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:18</t>
+          <t>2026-08-31 22:23:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:19</t>
+          <t>2026-08-31 22:23:18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:19</t>
+          <t>2026-08-31 22:23:18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:19</t>
+          <t>2026-08-31 22:23:18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:19</t>
+          <t>2026-08-31 22:23:18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:31:19</t>
+          <t>2026-08-31 22:23:18</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
